--- a/output/pdf_financials_xlsx/IDEX.xlsx
+++ b/output/pdf_financials_xlsx/IDEX.xlsx
@@ -1649,10 +1649,10 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.010256</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.08771900000000001</v>
       </c>
     </row>
     <row r="93">
@@ -2780,7 +2780,11 @@
           <t>Warrants reserve 10</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E20" s="5" t="n">
         <v>0.010256</v>
       </c>

--- a/output/pdf_financials_xlsx/IDEX.xlsx
+++ b/output/pdf_financials_xlsx/IDEX.xlsx
@@ -553,10 +553,10 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.154932</v>
+        <v>1.813335</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.639373</v>
+        <v>3.072823</v>
       </c>
     </row>
     <row r="11">
@@ -566,10 +566,10 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-0.154932</v>
+        <v>-1.813335</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-0.639373</v>
+        <v>-3.072823</v>
       </c>
     </row>
     <row r="12">
@@ -887,10 +887,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.40048</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>1.603811</v>
       </c>
     </row>
     <row r="35">
@@ -913,10 +913,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0.05</v>
+        <v>0.45048</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>1.603811</v>
       </c>
     </row>
     <row r="37">
@@ -1069,10 +1069,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.717466</v>
+        <v>0.316986</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>2.644289</v>
+        <v>1.040478</v>
       </c>
     </row>
     <row r="49">
@@ -2062,7 +2062,7 @@
         <v>0</v>
       </c>
       <c r="C124" s="3" t="n">
-        <v>0</v>
+        <v>-0.003406</v>
       </c>
     </row>
     <row r="125">
@@ -2075,7 +2075,7 @@
         <v>0</v>
       </c>
       <c r="C125" s="3" t="n">
-        <v>0</v>
+        <v>-0.003406</v>
       </c>
     </row>
     <row r="126">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -2418,7 +2418,11 @@
           <t>Reclamation deposits 7</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>-</t>
@@ -3364,7 +3368,11 @@
           <t>Cash paid for reclamation deposits 7</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
           <t>-</t>
@@ -3500,7 +3508,11 @@
           <t>Lease payments 8</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E47" t="inlineStr">
         <is>
           <t>-</t>
@@ -4066,14 +4078,14 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E68" s="5" t="n">
-        <v>-1.813335</v>
+        <v>1.813335</v>
       </c>
       <c r="F68" s="5" t="n">
-        <v>-3.072823</v>
+        <v>3.072823</v>
       </c>
     </row>
     <row r="69">

--- a/output/pdf_financials_xlsx/IDEX.xlsx
+++ b/output/pdf_financials_xlsx/IDEX.xlsx
@@ -1362,7 +1362,7 @@
         <v>0</v>
       </c>
       <c r="C70" s="3" t="n">
-        <v>0</v>
+        <v>0.027165</v>
       </c>
     </row>
     <row r="71">
@@ -1375,7 +1375,7 @@
         <v>0</v>
       </c>
       <c r="C71" s="3" t="n">
-        <v>0</v>
+        <v>0.027165</v>
       </c>
     </row>
     <row r="72">
@@ -1427,7 +1427,7 @@
         <v>0</v>
       </c>
       <c r="C75" s="3" t="n">
-        <v>0.027165</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -1493,10 +1493,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C80" s="3" t="n">
+        <v>0.008459025030804677</v>
       </c>
     </row>
     <row r="81">
@@ -1945,7 +1943,7 @@
         <v>0</v>
       </c>
       <c r="C115" s="3" t="n">
-        <v>0</v>
+        <v>0.084773</v>
       </c>
     </row>
     <row r="116">
@@ -2618,7 +2616,11 @@
           <t>Current portion of lease obligation 8</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>-</t>
@@ -3424,7 +3426,11 @@
           <t>Proceeds from sale of marketable securities 4</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E44" t="inlineStr">
         <is>
           <t>-</t>
